--- a/ML_Topics_Codes_Saifur/Linear_Regression/Simple_Linear_Regression/prediction.xlsx
+++ b/ML_Topics_Codes_Saifur/Linear_Regression/Simple_Linear_Regression/prediction.xlsx
@@ -425,183 +425,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
+      <c r="A2" t="n">
+        <v>2600</v>
       </c>
       <c r="B2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="C2" t="n">
         <v>533664.3835616438</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
+      <c r="A3" t="n">
+        <v>3000</v>
       </c>
       <c r="B3" t="n">
+        <v>587979.4520547945</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3200</v>
+      </c>
+      <c r="B4" t="n">
+        <v>615136.9863013698</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="B5" t="n">
+        <v>669452.0547945206</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="B6" t="n">
+        <v>723767.1232876712</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B7" t="n">
+        <v>859554.7945205481</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="B8" t="n">
+        <v>995342.4657534247</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7000</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1131130.136986302</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>655873.2876712328</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>520085.6164383562</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2900</v>
+      </c>
+      <c r="B12" t="n">
+        <v>574400.6849315069</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B13" t="n">
+        <v>696609.5890410959</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4700</v>
+      </c>
+      <c r="B14" t="n">
+        <v>818818.493150685</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5600</v>
+      </c>
+      <c r="B15" t="n">
+        <v>941027.397260274</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>3000</v>
       </c>
-      <c r="C3" t="n">
-        <v>587979.4520547945</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C4" t="n">
-        <v>615136.9863013698</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C5" t="n">
-        <v>669452.0547945206</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C6" t="n">
-        <v>723767.1232876712</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4001</v>
-      </c>
-      <c r="C7" t="n">
-        <v>723902.9109589041</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4002</v>
-      </c>
-      <c r="C8" t="n">
-        <v>724038.6986301369</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2600</v>
-      </c>
-      <c r="C9" t="n">
-        <v>533664.3835616438</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C10" t="n">
-        <v>587979.4520547945</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C11" t="n">
-        <v>669452.0547945206</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C12" t="n">
-        <v>723767.1232876712</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>4001</v>
-      </c>
-      <c r="C13" t="n">
-        <v>723902.9109589041</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>4002</v>
-      </c>
-      <c r="C14" t="n">
-        <v>724038.6986301369</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2600</v>
-      </c>
-      <c r="C15" t="n">
-        <v>533664.3835616438</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="B16" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C16" t="n">
         <v>587979.4520547945</v>
       </c>
     </row>

--- a/ML_Topics_Codes_Saifur/Linear_Regression/Simple_Linear_Regression/prediction.xlsx
+++ b/ML_Topics_Codes_Saifur/Linear_Regression/Simple_Linear_Regression/prediction.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>2600</v>
       </c>
       <c r="B2" t="n">
-        <v>533664.3835616438</v>
+        <v>524151.2345679012</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>3000</v>
       </c>
       <c r="B3" t="n">
-        <v>587979.4520547945</v>
+        <v>589830.2469135802</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>3200</v>
       </c>
       <c r="B4" t="n">
-        <v>615136.9863013698</v>
+        <v>622669.7530864198</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3600</v>
       </c>
       <c r="B5" t="n">
-        <v>669452.0547945206</v>
+        <v>688348.7654320986</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4000</v>
       </c>
       <c r="B6" t="n">
-        <v>723767.1232876712</v>
+        <v>754027.7777777778</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5000</v>
       </c>
       <c r="B7" t="n">
-        <v>859554.7945205481</v>
+        <v>918225.3086419753</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6000</v>
       </c>
       <c r="B8" t="n">
-        <v>995342.4657534247</v>
+        <v>1082422.839506173</v>
       </c>
     </row>
     <row r="9">
@@ -501,63 +501,7 @@
         <v>7000</v>
       </c>
       <c r="B9" t="n">
-        <v>1131130.136986302</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>3500</v>
-      </c>
-      <c r="B10" t="n">
-        <v>655873.2876712328</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="B11" t="n">
-        <v>520085.6164383562</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2900</v>
-      </c>
-      <c r="B12" t="n">
-        <v>574400.6849315069</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3800</v>
-      </c>
-      <c r="B13" t="n">
-        <v>696609.5890410959</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>4700</v>
-      </c>
-      <c r="B14" t="n">
-        <v>818818.493150685</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>5600</v>
-      </c>
-      <c r="B15" t="n">
-        <v>941027.397260274</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B16" t="n">
-        <v>587979.4520547945</v>
+        <v>1246620.37037037</v>
       </c>
     </row>
   </sheetData>
